--- a/apps/api/assets/vocabulary/初中/外研版/外研版初中英语九年级下册.xlsx
+++ b/apps/api/assets/vocabulary/初中/外研版/外研版初中英语九年级下册.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D129"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -501,6 +501,16 @@
           <t>because of</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 因
@@ -587,6 +597,16 @@
           <t>as long as</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">conj. 只要
@@ -642,6 +662,16 @@
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>take care</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -919,6 +949,16 @@
           <t>secondary school</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 中学；中等学校
@@ -1024,6 +1064,16 @@
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>used to</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1136,6 +1186,16 @@
           <t>spare time</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 业余时间；业余的
@@ -1147,6 +1207,16 @@
       <c r="A33" s="2" t="inlineStr">
         <is>
           <t>speak up</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1582,6 +1652,16 @@
           <t>go off</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 进行得 (well； badly)；(话等)冒出
@@ -1643,6 +1723,16 @@
           <t>in one go</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 一口气
@@ -1679,6 +1769,16 @@
       <c r="A57" s="2" t="inlineStr">
         <is>
           <t>rock climbing</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -1842,6 +1942,16 @@
       <c r="A64" s="2" t="inlineStr">
         <is>
           <t>fall asleep</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -2126,6 +2236,16 @@
           <t>call off</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 〈口〉命令停止；丢手；取消(婚约)；〈美〉点(名)
@@ -2139,6 +2259,16 @@
           <t>thanks to</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 感谢；幸亏；多亏
@@ -2152,6 +2282,16 @@
           <t>health care</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 医疗保健；医疗卫生
@@ -2253,6 +2393,16 @@
       <c r="A83" s="2" t="inlineStr">
         <is>
           <t>once in a while</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -2410,6 +2560,16 @@
           <t>heat up</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 加热；加剧；变得激烈
@@ -2703,6 +2863,16 @@
       <c r="A103" s="2" t="inlineStr">
         <is>
           <t>help yourself</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -3144,6 +3314,16 @@
           <t>laugh at</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 嘲笑；付之一笑；因…而发笑
@@ -3180,6 +3360,16 @@
           <t>give up</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 放弃；断绝；投降；自首
@@ -3191,6 +3381,16 @@
       <c r="A125" s="2" t="inlineStr">
         <is>
           <t>try one's best</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
